--- a/Resultados/RESULTADOS.xlsx
+++ b/Resultados/RESULTADOS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hade\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CBF10533-2BC9-41A1-942F-B3A66BC555A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E56E219-A0ED-4E43-882C-0CAD865109D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{3B675853-32B9-49D2-A84A-33154E62B4F8}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{3B675853-32B9-49D2-A84A-33154E62B4F8}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -347,15 +347,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -716,52 +713,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" ht="16.5" x14ac:dyDescent="0.4">
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="J1" s="15" t="s">
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="J1" s="12" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="J2" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="K2" s="13" t="s">
+      <c r="K2" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="L2" s="13" t="s">
+      <c r="L2" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="M2" s="13" t="s">
+      <c r="M2" s="10" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -779,13 +776,13 @@
       <c r="G3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="J3" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="K3" s="16" t="s">
+      <c r="K3" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="L3" s="18" t="s">
+      <c r="L3" s="15" t="s">
         <v>56</v>
       </c>
       <c r="M3" s="1" t="s">
@@ -793,7 +790,7 @@
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -811,10 +808,10 @@
       <c r="G4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="J4" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="K4" s="17" t="s">
+      <c r="K4" s="14" t="s">
         <v>52</v>
       </c>
       <c r="L4" s="1" t="s">
@@ -825,7 +822,7 @@
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -843,10 +840,10 @@
       <c r="G5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J5" s="14" t="s">
+      <c r="J5" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="K5" s="17" t="s">
+      <c r="K5" s="14" t="s">
         <v>53</v>
       </c>
       <c r="L5" s="1" t="s">
@@ -857,7 +854,7 @@
       </c>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -875,10 +872,10 @@
       <c r="G6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J6" s="14" t="s">
+      <c r="J6" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="K6" s="17" t="s">
+      <c r="K6" s="14" t="s">
         <v>54</v>
       </c>
       <c r="L6" s="1" t="s">
@@ -889,16 +886,10 @@
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="J7" s="14" t="s">
+      <c r="J7" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="K7" s="17" t="s">
+      <c r="K7" s="14" t="s">
         <v>55</v>
       </c>
       <c r="L7" s="1" t="s">
@@ -909,37 +900,37 @@
       </c>
     </row>
     <row r="8" spans="2:13" ht="16.5" x14ac:dyDescent="0.4">
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="6" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="7" t="s">
         <v>34</v>
       </c>
       <c r="C10" s="1">
-        <v>180511</v>
-      </c>
-      <c r="D10" s="12" t="s">
+        <v>180519</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>38</v>
       </c>
       <c r="E10" s="1" t="s">
@@ -947,13 +938,13 @@
       </c>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="7" t="s">
         <v>35</v>
       </c>
       <c r="C11" s="1">
-        <v>98973</v>
-      </c>
-      <c r="D11" s="12" t="s">
+        <v>98977</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>39</v>
       </c>
       <c r="E11" s="1" t="s">
@@ -961,7 +952,7 @@
       </c>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="7" t="s">
         <v>36</v>
       </c>
       <c r="C12" s="1">
@@ -975,11 +966,11 @@
       </c>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="7" t="s">
         <v>37</v>
       </c>
       <c r="C13" s="1">
-        <v>3.4976699999999998</v>
+        <v>3.4976530000000001</v>
       </c>
       <c r="D13" s="1">
         <v>3.5</v>
@@ -989,7 +980,7 @@
       </c>
     </row>
     <row r="15" spans="2:13" ht="16.5" x14ac:dyDescent="0.4">
-      <c r="B15" s="11"/>
+      <c r="B15" s="8"/>
     </row>
     <row r="18" ht="25.5" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
